--- a/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
+++ b/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
@@ -1,90 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Statistical data analysis/Plots of Cu Toxicity/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_924DA130869E2F2C54BFAC9C1C2533C62AD0974E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF9C5D09-48CB-4F68-A8D7-894AAA18FC6D}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="1990" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw variables" sheetId="1" r:id="rId1"/>
-    <sheet name="Log10 variables" sheetId="2" r:id="rId2"/>
+    <sheet name="Raw variables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Log10 variables" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="19">
-  <si>
-    <t>Typology</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>mle_mean</t>
-  </si>
-  <si>
-    <t>mle_variance</t>
-  </si>
-  <si>
-    <t>mle_sd</t>
-  </si>
-  <si>
-    <t>Pooled Water</t>
-  </si>
-  <si>
-    <t>Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t>Perennial Tribs</t>
-  </si>
-  <si>
-    <t>Developed Tribs</t>
-  </si>
-  <si>
-    <t>Main Stem</t>
-  </si>
-  <si>
-    <t>Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>Cu_Acute_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Acute_Tox_Minnow_nM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Typology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Acute_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Acute_Tox_Minnow_nM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -120,15 +113,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -410,16 +394,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,418 +418,418 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>30</v>
       </c>
-      <c r="D2">
-        <v>149.57659528747101</v>
-      </c>
-      <c r="E2">
-        <v>31126.546017607201</v>
-      </c>
-      <c r="F2">
-        <v>176.42716915942199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D2" t="n">
+        <v>149.576595287471</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31126.5460176072</v>
+      </c>
+      <c r="F2" t="n">
+        <v>176.427169159422</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>14</v>
       </c>
-      <c r="D3">
-        <v>87.065376368806398</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="n">
+        <v>87.0653763688064</v>
+      </c>
+      <c r="E3" t="n">
         <v>26146.8564072466</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>161.69989612627</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>93</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>115.304374659939</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>3194.69626311401</v>
       </c>
-      <c r="F4">
-        <v>56.521644200376997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" t="n">
+        <v>56.521644200377</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>122</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>60.208491161763</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1610.52197268746</v>
       </c>
-      <c r="F5">
-        <v>40.131309132489797</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" t="n">
+        <v>40.1313091324898</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>127</v>
       </c>
-      <c r="D6">
-        <v>254.42723511567101</v>
-      </c>
-      <c r="E6">
-        <v>24619.986013837199</v>
-      </c>
-      <c r="F6">
+      <c r="D6" t="n">
+        <v>254.427235115671</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24619.9860138372</v>
+      </c>
+      <c r="F6" t="n">
         <v>156.907571563125</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7">
-        <v>560.17073942390005</v>
-      </c>
-      <c r="E7">
-        <v>356465.38433137501</v>
-      </c>
-      <c r="F7">
-        <v>597.04722119056498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D7" t="n">
+        <v>560.1707394239</v>
+      </c>
+      <c r="E7" t="n">
+        <v>356465.384331375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>597.047221190565</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>305.51248464405501</v>
-      </c>
-      <c r="E8">
+      <c r="D8" t="n">
+        <v>305.512484644055</v>
+      </c>
+      <c r="E8" t="n">
         <v>323101.012405049</v>
       </c>
-      <c r="F8">
-        <v>568.41975018910898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" t="n">
+        <v>568.419750189109</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>93</v>
       </c>
-      <c r="D9">
-        <v>429.06456186791701</v>
-      </c>
-      <c r="E9">
+      <c r="D9" t="n">
+        <v>429.064561867917</v>
+      </c>
+      <c r="E9" t="n">
         <v>42554.4547154662</v>
       </c>
-      <c r="F9">
-        <v>206.28731108690701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" t="n">
+        <v>206.287311086907</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>122</v>
       </c>
-      <c r="D10">
-        <v>228.44107963376899</v>
-      </c>
-      <c r="E10">
+      <c r="D10" t="n">
+        <v>228.441079633769</v>
+      </c>
+      <c r="E10" t="n">
         <v>18729.694008863</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>136.856472294382</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>127</v>
       </c>
-      <c r="D11">
-        <v>848.44613076611301</v>
-      </c>
-      <c r="E11">
+      <c r="D11" t="n">
+        <v>848.446130766113</v>
+      </c>
+      <c r="E11" t="n">
         <v>180953.676786355</v>
       </c>
-      <c r="F11">
-        <v>425.38650282578902</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" t="n">
+        <v>425.386502825789</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D12">
-        <v>680.02659456093795</v>
-      </c>
-      <c r="E12">
-        <v>504093.81793174701</v>
-      </c>
-      <c r="F12">
-        <v>709.99564641745997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12" t="n">
+        <v>680.026594560938</v>
+      </c>
+      <c r="E12" t="n">
+        <v>504093.817931747</v>
+      </c>
+      <c r="F12" t="n">
+        <v>709.99564641746</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>14</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>368.25443037815</v>
       </c>
-      <c r="E13">
-        <v>471442.45039828698</v>
-      </c>
-      <c r="F13">
-        <v>686.61666918178298</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E13" t="n">
+        <v>471442.450398287</v>
+      </c>
+      <c r="F13" t="n">
+        <v>686.616669181783</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>93</v>
       </c>
-      <c r="D14">
-        <v>518.06755049340404</v>
-      </c>
-      <c r="E14">
-        <v>61764.561038428998</v>
-      </c>
-      <c r="F14">
-        <v>248.52476946660499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14" t="n">
+        <v>518.067550493404</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61764.561038429</v>
+      </c>
+      <c r="F14" t="n">
+        <v>248.524769466605</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>122</v>
       </c>
-      <c r="D15">
-        <v>277.79655635210099</v>
-      </c>
-      <c r="E15">
-        <v>26313.315334995099</v>
-      </c>
-      <c r="F15">
-        <v>162.21379514392501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" t="n">
+        <v>277.796556352101</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26313.3153349951</v>
+      </c>
+      <c r="F15" t="n">
+        <v>162.213795143925</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>127</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1002.48478645874</v>
       </c>
-      <c r="E16">
-        <v>240468.12562427099</v>
-      </c>
-      <c r="F16">
-        <v>490.37549451850799</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E16" t="n">
+        <v>240468.125624271</v>
+      </c>
+      <c r="F16" t="n">
+        <v>490.375494518508</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>30</v>
       </c>
-      <c r="D17">
-        <v>1743.3766515750899</v>
-      </c>
-      <c r="E17">
-        <v>2583035.3126167599</v>
-      </c>
-      <c r="F17">
+      <c r="D17" t="n">
+        <v>1743.37665157509</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2583035.31261676</v>
+      </c>
+      <c r="F17" t="n">
         <v>1607.18241423205</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>14</v>
       </c>
-      <c r="D18">
-        <v>911.55374905481096</v>
-      </c>
-      <c r="E18">
-        <v>2946622.5656366101</v>
-      </c>
-      <c r="F18">
+      <c r="D18" t="n">
+        <v>911.553749054811</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2946622.56563661</v>
+      </c>
+      <c r="F18" t="n">
         <v>1716.57291299747</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>93</v>
       </c>
-      <c r="D19">
-        <v>1267.8793817175199</v>
-      </c>
-      <c r="E19">
+      <c r="D19" t="n">
+        <v>1267.87938171752</v>
+      </c>
+      <c r="E19" t="n">
         <v>357480.231367581</v>
       </c>
-      <c r="F19">
-        <v>597.89650556562196</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" t="n">
+        <v>597.896505565622</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>122</v>
       </c>
-      <c r="D20">
-        <v>759.21585608482201</v>
-      </c>
-      <c r="E20">
-        <v>133375.17223748899</v>
-      </c>
-      <c r="F20">
-        <v>365.20565745547901</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D20" t="n">
+        <v>759.215856084822</v>
+      </c>
+      <c r="E20" t="n">
+        <v>133375.172237489</v>
+      </c>
+      <c r="F20" t="n">
+        <v>365.205657455479</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>127</v>
       </c>
-      <c r="D21">
-        <v>2218.7981947919998</v>
-      </c>
-      <c r="E21">
+      <c r="D21" t="n">
+        <v>2218.798194792</v>
+      </c>
+      <c r="E21" t="n">
         <v>937885.188945845</v>
       </c>
-      <c r="F21">
-        <v>968.44472684084803</v>
+      <c r="F21" t="n">
+        <v>968.444726840848</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -870,408 +849,408 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>30</v>
       </c>
-      <c r="D2">
-        <v>1.9225464311546101</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>1.92254643115461</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.218174879324149</v>
       </c>
-      <c r="F2">
-        <v>0.46709193883447497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" t="n">
+        <v>0.467091938834475</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>14</v>
       </c>
-      <c r="D3">
-        <v>1.5627425141518301</v>
-      </c>
-      <c r="E3">
-        <v>0.31239881678759501</v>
-      </c>
-      <c r="F3">
-        <v>0.55892648603156703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D3" t="n">
+        <v>1.56274251415183</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.312398816787595</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.558926486031567</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>93</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>2.00055782628377</v>
       </c>
-      <c r="E4">
-        <v>6.4923836871697505E-2</v>
-      </c>
-      <c r="F4">
-        <v>0.25480156371517299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E4" t="n">
+        <v>0.0649238368716975</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.254801563715173</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>122</v>
       </c>
-      <c r="D5">
-        <v>1.6766039169179601</v>
-      </c>
-      <c r="E5">
-        <v>0.10150426932769401</v>
-      </c>
-      <c r="F5">
+      <c r="D5" t="n">
+        <v>1.67660391691796</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.101504269327694</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.318597346705358</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>127</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>2.34709147409529</v>
       </c>
-      <c r="E6">
-        <v>4.5092966790277703E-2</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>0.0450929667902777</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.212351046124755</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7">
-        <v>2.5294804112681999</v>
-      </c>
-      <c r="E7">
+      <c r="D7" t="n">
+        <v>2.5294804112682</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.190803741305823</v>
       </c>
-      <c r="F7">
-        <v>0.43681087590148598</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" t="n">
+        <v>0.436810875901486</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>2.1335158593424701</v>
-      </c>
-      <c r="E8">
+      <c r="D8" t="n">
+        <v>2.13351585934247</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.262722491251693</v>
       </c>
-      <c r="F8">
-        <v>0.51256462153731697</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" t="n">
+        <v>0.512564621537317</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>93</v>
       </c>
-      <c r="D9">
-        <v>2.5740081974515001</v>
-      </c>
-      <c r="E9">
-        <v>6.11006572007659E-2</v>
-      </c>
-      <c r="F9">
+      <c r="D9" t="n">
+        <v>2.5740081974515</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0611006572007659</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.247185471257446</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>122</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>2.27233114857547</v>
       </c>
-      <c r="E10">
-        <v>8.5113388206606799E-2</v>
-      </c>
-      <c r="F10">
+      <c r="E10" t="n">
+        <v>0.0851133882066068</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.291741989104426</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>127</v>
       </c>
-      <c r="D11">
-        <v>2.8851888120083999</v>
-      </c>
-      <c r="E11">
-        <v>3.4979395101133397E-2</v>
-      </c>
-      <c r="F11">
-        <v>0.18702779232278099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11" t="n">
+        <v>2.8851888120084</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0349793951011334</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.187027792322781</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D12">
-        <v>2.6209948636256502</v>
-      </c>
-      <c r="E12">
+      <c r="D12" t="n">
+        <v>2.62099486362565</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.184437537224662</v>
       </c>
-      <c r="F12">
-        <v>0.42946191591881799</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" t="n">
+        <v>0.429461915918818</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>14</v>
       </c>
-      <c r="D13">
-        <v>2.2193146546675901</v>
-      </c>
-      <c r="E13">
-        <v>0.25323668460068899</v>
-      </c>
-      <c r="F13">
-        <v>0.50322627574550305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13" t="n">
+        <v>2.21931465466759</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.253236684600689</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.503226275745503</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>93</v>
       </c>
-      <c r="D14">
-        <v>2.6564696543667901</v>
-      </c>
-      <c r="E14">
-        <v>6.0169300850449199E-2</v>
-      </c>
-      <c r="F14">
-        <v>0.24529431475362201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14" t="n">
+        <v>2.65646965436679</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0601693008504492</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.245294314753622</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>122</v>
       </c>
-      <c r="D15">
-        <v>2.3612604232377699</v>
-      </c>
-      <c r="E15">
-        <v>8.1093164914012195E-2</v>
-      </c>
-      <c r="F15">
-        <v>0.28476861644853402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" t="n">
+        <v>2.36126042323777</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0810931649140122</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.284768616448534</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>127</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>2.95955884777573</v>
       </c>
-      <c r="E16">
-        <v>3.3503105942530198E-2</v>
-      </c>
-      <c r="F16">
-        <v>0.18303853676898299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E16" t="n">
+        <v>0.0335031059425302</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.183038536768983</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>30</v>
       </c>
-      <c r="D17">
-        <v>3.0802621972937101</v>
-      </c>
-      <c r="E17">
-        <v>0.13757594562961101</v>
-      </c>
-      <c r="F17">
-        <v>0.37091231528436902</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D17" t="n">
+        <v>3.08026219729371</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.137575945629611</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.370912315284369</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>14</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>2.64359457653658</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>0.198740814758568</v>
       </c>
-      <c r="F18">
-        <v>0.44580356072890198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" t="n">
+        <v>0.445803560728902</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>93</v>
       </c>
-      <c r="D19">
-        <v>3.0493254567623702</v>
-      </c>
-      <c r="E19">
-        <v>5.3666040848864199E-2</v>
-      </c>
-      <c r="F19">
+      <c r="D19" t="n">
+        <v>3.04932545676237</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0536660408488642</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.231659320660457</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>122</v>
       </c>
-      <c r="D20">
-        <v>2.8233166142807198</v>
-      </c>
-      <c r="E20">
-        <v>5.5539854361990097E-2</v>
-      </c>
-      <c r="F20">
+      <c r="D20" t="n">
+        <v>2.82331661428072</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0555398543619901</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.235668950780518</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>127</v>
       </c>
-      <c r="D21">
-        <v>3.3136461358092402</v>
-      </c>
-      <c r="E21">
-        <v>2.5968969869400001E-2</v>
-      </c>
-      <c r="F21">
+      <c r="D21" t="n">
+        <v>3.31364613580924</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0259689698694</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.161148905889553</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
+++ b/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
@@ -1,83 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Statistical data analysis/Plots of Cu Toxicity/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_924DA130D9B66145625DBB9C1C2533C62AD09770" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16C9E8CD-4C4A-4681-BA37-0312E54EDB43}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw variables" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Log10 variables" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw variables" sheetId="1" r:id="rId1"/>
+    <sheet name="Log10 variables" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mle_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mle_variance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mle_sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_Acute_Tox_Minnow_nM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="19">
+  <si>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>mle_mean</t>
+  </si>
+  <si>
+    <t>mle_variance</t>
+  </si>
+  <si>
+    <t>mle_sd</t>
+  </si>
+  <si>
+    <t>Pooled</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>Non-Perennial</t>
+  </si>
+  <si>
+    <t>Perennial</t>
+  </si>
+  <si>
+    <t>Developed Perennial</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t>log_Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>log_Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>log_Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t>log_Cu_Acute_Tox_Minnow_nM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -106,13 +116,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -394,11 +415,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -418,418 +443,422 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30</v>
       </c>
-      <c r="D2" t="n">
-        <v>149.576595287471</v>
-      </c>
-      <c r="E2" t="n">
-        <v>31126.5460176072</v>
-      </c>
-      <c r="F2" t="n">
-        <v>176.427169159422</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2">
+        <v>149.57659528747101</v>
+      </c>
+      <c r="E2">
+        <v>31126.546017607201</v>
+      </c>
+      <c r="F2">
+        <v>176.42716915942199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>14</v>
       </c>
-      <c r="D3" t="n">
-        <v>87.0653763688064</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3">
+        <v>87.065376368806398</v>
+      </c>
+      <c r="E3">
         <v>26146.8564072466</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>161.69989612627</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>93</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>115.304374659939</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>3194.69626311401</v>
       </c>
-      <c r="F4" t="n">
-        <v>56.521644200377</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4">
+        <v>56.521644200376997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>122</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>60.208491161763</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1610.52197268746</v>
       </c>
-      <c r="F5" t="n">
-        <v>40.1313091324898</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5">
+        <v>40.131309132489797</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>127</v>
       </c>
-      <c r="D6" t="n">
-        <v>254.427235115671</v>
-      </c>
-      <c r="E6" t="n">
-        <v>24619.9860138372</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6">
+        <v>254.42723511567101</v>
+      </c>
+      <c r="E6">
+        <v>24619.986013837199</v>
+      </c>
+      <c r="F6">
         <v>156.907571563125</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>30</v>
       </c>
-      <c r="D7" t="n">
-        <v>560.1707394239</v>
-      </c>
-      <c r="E7" t="n">
-        <v>356465.384331375</v>
-      </c>
-      <c r="F7" t="n">
-        <v>597.047221190565</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7">
+        <v>560.17073942390005</v>
+      </c>
+      <c r="E7">
+        <v>356465.38433137501</v>
+      </c>
+      <c r="F7">
+        <v>597.04722119056498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8" t="n">
-        <v>305.512484644055</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8">
+        <v>305.51248464405501</v>
+      </c>
+      <c r="E8">
         <v>323101.012405049</v>
       </c>
-      <c r="F8" t="n">
-        <v>568.419750189109</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8">
+        <v>568.41975018910898</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>93</v>
       </c>
-      <c r="D9" t="n">
-        <v>429.064561867917</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9">
+        <v>429.06456186791701</v>
+      </c>
+      <c r="E9">
         <v>42554.4547154662</v>
       </c>
-      <c r="F9" t="n">
-        <v>206.287311086907</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9">
+        <v>206.28731108690701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>122</v>
       </c>
-      <c r="D10" t="n">
-        <v>228.441079633769</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10">
+        <v>228.44107963376899</v>
+      </c>
+      <c r="E10">
         <v>18729.694008863</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>136.856472294382</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>127</v>
       </c>
-      <c r="D11" t="n">
-        <v>848.446130766113</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11">
+        <v>848.44613076611301</v>
+      </c>
+      <c r="E11">
         <v>180953.676786355</v>
       </c>
-      <c r="F11" t="n">
-        <v>425.386502825789</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11">
+        <v>425.38650282578902</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>30</v>
       </c>
-      <c r="D12" t="n">
-        <v>680.026594560938</v>
-      </c>
-      <c r="E12" t="n">
-        <v>504093.817931747</v>
-      </c>
-      <c r="F12" t="n">
-        <v>709.99564641746</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="D12">
+        <v>680.02659456093795</v>
+      </c>
+      <c r="E12">
+        <v>504093.81793174701</v>
+      </c>
+      <c r="F12">
+        <v>709.99564641745997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>14</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>368.25443037815</v>
       </c>
-      <c r="E13" t="n">
-        <v>471442.450398287</v>
-      </c>
-      <c r="F13" t="n">
-        <v>686.616669181783</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="E13">
+        <v>471442.45039828698</v>
+      </c>
+      <c r="F13">
+        <v>686.61666918178298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>93</v>
       </c>
-      <c r="D14" t="n">
-        <v>518.067550493404</v>
-      </c>
-      <c r="E14" t="n">
-        <v>61764.561038429</v>
-      </c>
-      <c r="F14" t="n">
-        <v>248.524769466605</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="D14">
+        <v>518.06755049340404</v>
+      </c>
+      <c r="E14">
+        <v>61764.561038428998</v>
+      </c>
+      <c r="F14">
+        <v>248.52476946660499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>122</v>
       </c>
-      <c r="D15" t="n">
-        <v>277.796556352101</v>
-      </c>
-      <c r="E15" t="n">
-        <v>26313.3153349951</v>
-      </c>
-      <c r="F15" t="n">
-        <v>162.213795143925</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="D15">
+        <v>277.79655635210099</v>
+      </c>
+      <c r="E15">
+        <v>26313.315334995099</v>
+      </c>
+      <c r="F15">
+        <v>162.21379514392501</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>127</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>1002.48478645874</v>
       </c>
-      <c r="E16" t="n">
-        <v>240468.125624271</v>
-      </c>
-      <c r="F16" t="n">
-        <v>490.375494518508</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16">
+        <v>240468.12562427099</v>
+      </c>
+      <c r="F16">
+        <v>490.37549451850799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>30</v>
       </c>
-      <c r="D17" t="n">
-        <v>1743.37665157509</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2583035.31261676</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="D17">
+        <v>1743.3766515750899</v>
+      </c>
+      <c r="E17">
+        <v>2583035.3126167599</v>
+      </c>
+      <c r="F17">
         <v>1607.18241423205</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>14</v>
       </c>
-      <c r="D18" t="n">
-        <v>911.553749054811</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2946622.56563661</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="D18">
+        <v>911.55374905481096</v>
+      </c>
+      <c r="E18">
+        <v>2946622.5656366101</v>
+      </c>
+      <c r="F18">
         <v>1716.57291299747</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>93</v>
       </c>
-      <c r="D19" t="n">
-        <v>1267.87938171752</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19">
+        <v>1267.8793817175199</v>
+      </c>
+      <c r="E19">
         <v>357480.231367581</v>
       </c>
-      <c r="F19" t="n">
-        <v>597.896505565622</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="F19">
+        <v>597.89650556562196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>122</v>
       </c>
-      <c r="D20" t="n">
-        <v>759.215856084822</v>
-      </c>
-      <c r="E20" t="n">
-        <v>133375.172237489</v>
-      </c>
-      <c r="F20" t="n">
-        <v>365.205657455479</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="D20">
+        <v>759.21585608482201</v>
+      </c>
+      <c r="E20">
+        <v>133375.17223748899</v>
+      </c>
+      <c r="F20">
+        <v>365.20565745547901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>127</v>
       </c>
-      <c r="D21" t="n">
-        <v>2218.798194792</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21">
+        <v>2218.7981947919998</v>
+      </c>
+      <c r="E21">
         <v>937885.188945845</v>
       </c>
-      <c r="F21" t="n">
-        <v>968.444726840848</v>
+      <c r="F21">
+        <v>968.44472684084803</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -849,408 +878,408 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.92254643115461</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" s="2">
+        <v>1.9225464311546101</v>
+      </c>
+      <c r="E2">
         <v>0.218174879324149</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.467091938834475</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="F2" s="1">
+        <v>0.46709193883447497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>14</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.56274251415183</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.312398816787595</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.558926486031567</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3" s="2">
+        <v>1.5627425141518301</v>
+      </c>
+      <c r="E3">
+        <v>0.31239881678759501</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.55892648603156703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>93</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2">
         <v>2.00055782628377</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.0649238368716975</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.254801563715173</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>6.4923836871697505E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.25480156371517299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>122</v>
       </c>
-      <c r="D5" t="n">
-        <v>1.67660391691796</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.101504269327694</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5" s="2">
+        <v>1.6766039169179601</v>
+      </c>
+      <c r="E5">
+        <v>0.10150426932769401</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.318597346705358</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>127</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2">
         <v>2.34709147409529</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.0450929667902777</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>4.5092966790277703E-2</v>
+      </c>
+      <c r="F6" s="1">
         <v>0.212351046124755</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>30</v>
       </c>
-      <c r="D7" t="n">
-        <v>2.5294804112682</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="2">
+        <v>2.5294804112681999</v>
+      </c>
+      <c r="E7">
         <v>0.190803741305823</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.436810875901486</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="F7" s="1">
+        <v>0.43681087590148598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8" t="n">
-        <v>2.13351585934247</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="2">
+        <v>2.1335158593424701</v>
+      </c>
+      <c r="E8">
         <v>0.262722491251693</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.512564621537317</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8" s="1">
+        <v>0.51256462153731697</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>93</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.5740081974515</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0611006572007659</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="D9" s="2">
+        <v>2.5740081974515001</v>
+      </c>
+      <c r="E9">
+        <v>6.11006572007659E-2</v>
+      </c>
+      <c r="F9" s="1">
         <v>0.247185471257446</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>122</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2">
         <v>2.27233114857547</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.0851133882066068</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10">
+        <v>8.5113388206606799E-2</v>
+      </c>
+      <c r="F10" s="1">
         <v>0.291741989104426</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>127</v>
       </c>
-      <c r="D11" t="n">
-        <v>2.8851888120084</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0349793951011334</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.187027792322781</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="D11" s="2">
+        <v>2.8851888120083999</v>
+      </c>
+      <c r="E11">
+        <v>3.4979395101133397E-2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.18702779232278099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>30</v>
       </c>
-      <c r="D12" t="n">
-        <v>2.62099486362565</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="2">
+        <v>2.6209948636256502</v>
+      </c>
+      <c r="E12">
         <v>0.184437537224662</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.429461915918818</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12" s="1">
+        <v>0.42946191591881799</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>14</v>
       </c>
-      <c r="D13" t="n">
-        <v>2.21931465466759</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.253236684600689</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.503226275745503</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="D13" s="2">
+        <v>2.2193146546675901</v>
+      </c>
+      <c r="E13">
+        <v>0.25323668460068899</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.50322627574550305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>93</v>
       </c>
-      <c r="D14" t="n">
-        <v>2.65646965436679</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0601693008504492</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.245294314753622</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="D14" s="2">
+        <v>2.6564696543667901</v>
+      </c>
+      <c r="E14">
+        <v>6.0169300850449199E-2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.24529431475362201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>122</v>
       </c>
-      <c r="D15" t="n">
-        <v>2.36126042323777</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0810931649140122</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.284768616448534</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="D15" s="2">
+        <v>2.3612604232377699</v>
+      </c>
+      <c r="E15">
+        <v>8.1093164914012195E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.28476861644853402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>127</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2">
         <v>2.95955884777573</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.0335031059425302</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.183038536768983</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16">
+        <v>3.3503105942530198E-2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.18303853676898299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>30</v>
       </c>
-      <c r="D17" t="n">
-        <v>3.08026219729371</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.137575945629611</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.370912315284369</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="D17" s="2">
+        <v>3.0802621972937101</v>
+      </c>
+      <c r="E17">
+        <v>0.13757594562961101</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.37091231528436902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>14</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2">
         <v>2.64359457653658</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.198740814758568</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.445803560728902</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="F18" s="1">
+        <v>0.44580356072890198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>93</v>
       </c>
-      <c r="D19" t="n">
-        <v>3.04932545676237</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0536660408488642</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="D19" s="2">
+        <v>3.0493254567623702</v>
+      </c>
+      <c r="E19">
+        <v>5.3666040848864199E-2</v>
+      </c>
+      <c r="F19" s="1">
         <v>0.231659320660457</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>122</v>
       </c>
-      <c r="D20" t="n">
-        <v>2.82331661428072</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0555398543619901</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="D20" s="2">
+        <v>2.8233166142807198</v>
+      </c>
+      <c r="E20">
+        <v>5.5539854361990097E-2</v>
+      </c>
+      <c r="F20" s="1">
         <v>0.235668950780518</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>127</v>
       </c>
-      <c r="D21" t="n">
-        <v>3.31364613580924</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.0259689698694</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="D21" s="2">
+        <v>3.3136461358092402</v>
+      </c>
+      <c r="E21">
+        <v>2.5968969869400001E-2</v>
+      </c>
+      <c r="F21" s="1">
         <v>0.161148905889553</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
+++ b/Copper/6. Statistical data analysis/Plots of Cu Toxicity/MLE_Cu_toxicity.xlsx
@@ -1,93 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Statistical data analysis/Plots of Cu Toxicity/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_924DA130D9B66145625DBB9C1C2533C62AD09770" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16C9E8CD-4C4A-4681-BA37-0312E54EDB43}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw variables" sheetId="1" r:id="rId1"/>
-    <sheet name="Log10 variables" sheetId="2" r:id="rId2"/>
+    <sheet name="Raw variables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Log10 variables" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="19">
-  <si>
-    <t>Typology</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>mle_mean</t>
-  </si>
-  <si>
-    <t>mle_variance</t>
-  </si>
-  <si>
-    <t>mle_sd</t>
-  </si>
-  <si>
-    <t>Pooled</t>
-  </si>
-  <si>
-    <t>Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>Non-Perennial</t>
-  </si>
-  <si>
-    <t>Perennial</t>
-  </si>
-  <si>
-    <t>Developed Perennial</t>
-  </si>
-  <si>
-    <t>Main Stem</t>
-  </si>
-  <si>
-    <t>Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>Cu_Acute_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t>log_Cu_Acute_Tox_Minnow_nM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve">Typology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mle_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu_Acute_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_Acute_Tox_Minnow_nM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -116,24 +106,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -415,15 +394,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,422 +418,418 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>30</v>
       </c>
-      <c r="D2">
-        <v>149.57659528747101</v>
-      </c>
-      <c r="E2">
-        <v>31126.546017607201</v>
-      </c>
-      <c r="F2">
-        <v>176.42716915942199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D2" t="n">
+        <v>149.576595287471</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31126.5460176072</v>
+      </c>
+      <c r="F2" t="n">
+        <v>176.427169159422</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>14</v>
       </c>
-      <c r="D3">
-        <v>87.065376368806398</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="n">
+        <v>87.0653763688064</v>
+      </c>
+      <c r="E3" t="n">
         <v>26146.8564072466</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>161.69989612627</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>93</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>115.304374659939</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>3194.69626311401</v>
       </c>
-      <c r="F4">
-        <v>56.521644200376997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" t="n">
+        <v>56.521644200377</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>122</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>60.208491161763</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1610.52197268746</v>
       </c>
-      <c r="F5">
-        <v>40.131309132489797</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" t="n">
+        <v>40.1313091324898</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>127</v>
       </c>
-      <c r="D6">
-        <v>254.42723511567101</v>
-      </c>
-      <c r="E6">
-        <v>24619.986013837199</v>
-      </c>
-      <c r="F6">
+      <c r="D6" t="n">
+        <v>254.427235115671</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24619.9860138372</v>
+      </c>
+      <c r="F6" t="n">
         <v>156.907571563125</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7">
-        <v>560.17073942390005</v>
-      </c>
-      <c r="E7">
-        <v>356465.38433137501</v>
-      </c>
-      <c r="F7">
-        <v>597.04722119056498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D7" t="n">
+        <v>560.1707394239</v>
+      </c>
+      <c r="E7" t="n">
+        <v>356465.384331375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>597.047221190565</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>305.51248464405501</v>
-      </c>
-      <c r="E8">
+      <c r="D8" t="n">
+        <v>305.512484644055</v>
+      </c>
+      <c r="E8" t="n">
         <v>323101.012405049</v>
       </c>
-      <c r="F8">
-        <v>568.41975018910898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" t="n">
+        <v>568.419750189109</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>93</v>
       </c>
-      <c r="D9">
-        <v>429.06456186791701</v>
-      </c>
-      <c r="E9">
+      <c r="D9" t="n">
+        <v>429.064561867917</v>
+      </c>
+      <c r="E9" t="n">
         <v>42554.4547154662</v>
       </c>
-      <c r="F9">
-        <v>206.28731108690701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" t="n">
+        <v>206.287311086907</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>122</v>
       </c>
-      <c r="D10">
-        <v>228.44107963376899</v>
-      </c>
-      <c r="E10">
+      <c r="D10" t="n">
+        <v>228.441079633769</v>
+      </c>
+      <c r="E10" t="n">
         <v>18729.694008863</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>136.856472294382</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>127</v>
       </c>
-      <c r="D11">
-        <v>848.44613076611301</v>
-      </c>
-      <c r="E11">
+      <c r="D11" t="n">
+        <v>848.446130766113</v>
+      </c>
+      <c r="E11" t="n">
         <v>180953.676786355</v>
       </c>
-      <c r="F11">
-        <v>425.38650282578902</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" t="n">
+        <v>425.386502825789</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D12">
-        <v>680.02659456093795</v>
-      </c>
-      <c r="E12">
-        <v>504093.81793174701</v>
-      </c>
-      <c r="F12">
-        <v>709.99564641745997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12" t="n">
+        <v>680.026594560938</v>
+      </c>
+      <c r="E12" t="n">
+        <v>504093.817931747</v>
+      </c>
+      <c r="F12" t="n">
+        <v>709.99564641746</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>14</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>368.25443037815</v>
       </c>
-      <c r="E13">
-        <v>471442.45039828698</v>
-      </c>
-      <c r="F13">
-        <v>686.61666918178298</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E13" t="n">
+        <v>471442.450398287</v>
+      </c>
+      <c r="F13" t="n">
+        <v>686.616669181783</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>93</v>
       </c>
-      <c r="D14">
-        <v>518.06755049340404</v>
-      </c>
-      <c r="E14">
-        <v>61764.561038428998</v>
-      </c>
-      <c r="F14">
-        <v>248.52476946660499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14" t="n">
+        <v>518.067550493404</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61764.561038429</v>
+      </c>
+      <c r="F14" t="n">
+        <v>248.524769466605</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>122</v>
       </c>
-      <c r="D15">
-        <v>277.79655635210099</v>
-      </c>
-      <c r="E15">
-        <v>26313.315334995099</v>
-      </c>
-      <c r="F15">
-        <v>162.21379514392501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" t="n">
+        <v>277.796556352101</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26313.3153349951</v>
+      </c>
+      <c r="F15" t="n">
+        <v>162.213795143925</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>127</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1002.48478645874</v>
       </c>
-      <c r="E16">
-        <v>240468.12562427099</v>
-      </c>
-      <c r="F16">
-        <v>490.37549451850799</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E16" t="n">
+        <v>240468.125624271</v>
+      </c>
+      <c r="F16" t="n">
+        <v>490.375494518508</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>30</v>
       </c>
-      <c r="D17">
-        <v>1743.3766515750899</v>
-      </c>
-      <c r="E17">
-        <v>2583035.3126167599</v>
-      </c>
-      <c r="F17">
+      <c r="D17" t="n">
+        <v>1743.37665157509</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2583035.31261676</v>
+      </c>
+      <c r="F17" t="n">
         <v>1607.18241423205</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>14</v>
       </c>
-      <c r="D18">
-        <v>911.55374905481096</v>
-      </c>
-      <c r="E18">
-        <v>2946622.5656366101</v>
-      </c>
-      <c r="F18">
+      <c r="D18" t="n">
+        <v>911.553749054811</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2946622.56563661</v>
+      </c>
+      <c r="F18" t="n">
         <v>1716.57291299747</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>93</v>
       </c>
-      <c r="D19">
-        <v>1267.8793817175199</v>
-      </c>
-      <c r="E19">
+      <c r="D19" t="n">
+        <v>1267.87938171752</v>
+      </c>
+      <c r="E19" t="n">
         <v>357480.231367581</v>
       </c>
-      <c r="F19">
-        <v>597.89650556562196</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" t="n">
+        <v>597.896505565622</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>122</v>
       </c>
-      <c r="D20">
-        <v>759.21585608482201</v>
-      </c>
-      <c r="E20">
-        <v>133375.17223748899</v>
-      </c>
-      <c r="F20">
-        <v>365.20565745547901</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D20" t="n">
+        <v>759.215856084822</v>
+      </c>
+      <c r="E20" t="n">
+        <v>133375.172237489</v>
+      </c>
+      <c r="F20" t="n">
+        <v>365.205657455479</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>127</v>
       </c>
-      <c r="D21">
-        <v>2218.7981947919998</v>
-      </c>
-      <c r="E21">
+      <c r="D21" t="n">
+        <v>2218.798194792</v>
+      </c>
+      <c r="E21" t="n">
         <v>937885.188945845</v>
       </c>
-      <c r="F21">
-        <v>968.44472684084803</v>
+      <c r="F21" t="n">
+        <v>968.444726840848</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -878,408 +849,408 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>30</v>
       </c>
-      <c r="D2" s="2">
-        <v>1.9225464311546101</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>1.92254643115461</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.218174879324149</v>
       </c>
-      <c r="F2" s="1">
-        <v>0.46709193883447497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" t="n">
+        <v>0.467091938834475</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>14</v>
       </c>
-      <c r="D3" s="2">
-        <v>1.5627425141518301</v>
-      </c>
-      <c r="E3">
-        <v>0.31239881678759501</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.55892648603156703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D3" t="n">
+        <v>1.56274251415183</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.312398816787595</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.558926486031567</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>93</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" t="n">
         <v>2.00055782628377</v>
       </c>
-      <c r="E4">
-        <v>6.4923836871697505E-2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.25480156371517299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E4" t="n">
+        <v>0.0649238368716975</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.254801563715173</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>122</v>
       </c>
-      <c r="D5" s="2">
-        <v>1.6766039169179601</v>
-      </c>
-      <c r="E5">
-        <v>0.10150426932769401</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="D5" t="n">
+        <v>1.67660391691796</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.101504269327694</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.318597346705358</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>127</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" t="n">
         <v>2.34709147409529</v>
       </c>
-      <c r="E6">
-        <v>4.5092966790277703E-2</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0.0450929667902777</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.212351046124755</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="2">
-        <v>2.5294804112681999</v>
-      </c>
-      <c r="E7">
+      <c r="D7" t="n">
+        <v>2.5294804112682</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.190803741305823</v>
       </c>
-      <c r="F7" s="1">
-        <v>0.43681087590148598</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" t="n">
+        <v>0.436810875901486</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="2">
-        <v>2.1335158593424701</v>
-      </c>
-      <c r="E8">
+      <c r="D8" t="n">
+        <v>2.13351585934247</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.262722491251693</v>
       </c>
-      <c r="F8" s="1">
-        <v>0.51256462153731697</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" t="n">
+        <v>0.512564621537317</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>93</v>
       </c>
-      <c r="D9" s="2">
-        <v>2.5740081974515001</v>
-      </c>
-      <c r="E9">
-        <v>6.11006572007659E-2</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="D9" t="n">
+        <v>2.5740081974515</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0611006572007659</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.247185471257446</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>122</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" t="n">
         <v>2.27233114857547</v>
       </c>
-      <c r="E10">
-        <v>8.5113388206606799E-2</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0.0851133882066068</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.291741989104426</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>127</v>
       </c>
-      <c r="D11" s="2">
-        <v>2.8851888120083999</v>
-      </c>
-      <c r="E11">
-        <v>3.4979395101133397E-2</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.18702779232278099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11" t="n">
+        <v>2.8851888120084</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0349793951011334</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.187027792322781</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D12" s="2">
-        <v>2.6209948636256502</v>
-      </c>
-      <c r="E12">
+      <c r="D12" t="n">
+        <v>2.62099486362565</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.184437537224662</v>
       </c>
-      <c r="F12" s="1">
-        <v>0.42946191591881799</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" t="n">
+        <v>0.429461915918818</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>14</v>
       </c>
-      <c r="D13" s="2">
-        <v>2.2193146546675901</v>
-      </c>
-      <c r="E13">
-        <v>0.25323668460068899</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.50322627574550305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13" t="n">
+        <v>2.21931465466759</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.253236684600689</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.503226275745503</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>93</v>
       </c>
-      <c r="D14" s="2">
-        <v>2.6564696543667901</v>
-      </c>
-      <c r="E14">
-        <v>6.0169300850449199E-2</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.24529431475362201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14" t="n">
+        <v>2.65646965436679</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0601693008504492</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.245294314753622</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>122</v>
       </c>
-      <c r="D15" s="2">
-        <v>2.3612604232377699</v>
-      </c>
-      <c r="E15">
-        <v>8.1093164914012195E-2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.28476861644853402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" t="n">
+        <v>2.36126042323777</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0810931649140122</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.284768616448534</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>127</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" t="n">
         <v>2.95955884777573</v>
       </c>
-      <c r="E16">
-        <v>3.3503105942530198E-2</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.18303853676898299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E16" t="n">
+        <v>0.0335031059425302</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.183038536768983</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>30</v>
       </c>
-      <c r="D17" s="2">
-        <v>3.0802621972937101</v>
-      </c>
-      <c r="E17">
-        <v>0.13757594562961101</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0.37091231528436902</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D17" t="n">
+        <v>3.08026219729371</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.137575945629611</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.370912315284369</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" t="n">
         <v>2.64359457653658</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>0.198740814758568</v>
       </c>
-      <c r="F18" s="1">
-        <v>0.44580356072890198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" t="n">
+        <v>0.445803560728902</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>93</v>
       </c>
-      <c r="D19" s="2">
-        <v>3.0493254567623702</v>
-      </c>
-      <c r="E19">
-        <v>5.3666040848864199E-2</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="D19" t="n">
+        <v>3.04932545676237</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0536660408488642</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.231659320660457</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>122</v>
       </c>
-      <c r="D20" s="2">
-        <v>2.8233166142807198</v>
-      </c>
-      <c r="E20">
-        <v>5.5539854361990097E-2</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="D20" t="n">
+        <v>2.82331661428072</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0555398543619901</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.235668950780518</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>127</v>
       </c>
-      <c r="D21" s="2">
-        <v>3.3136461358092402</v>
-      </c>
-      <c r="E21">
-        <v>2.5968969869400001E-2</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="D21" t="n">
+        <v>3.31364613580924</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0259689698694</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.161148905889553</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>